--- a/data/b_Optimierung/Grundmodell_opt_speicher_statistiken.xlsx
+++ b/data/b_Optimierung/Grundmodell_opt_speicher_statistiken.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HansisRasanterRaser\Desktop\UNI\000_DA\git\knEBiD\data\b_Optimierung\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{811EF95C-3619-4953-AF91-FEA55CAF73F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC822ED-E1F8-4001-A805-7E74538CFCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -449,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="25" customWidth="1"/>
@@ -630,6 +630,24 @@
         <v>3297158.7333333339</v>
       </c>
     </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <f>C2/1000</f>
+        <v>57.012294000000004</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <f t="shared" ref="C8:C9" si="2">C3/1000</f>
+        <v>304.3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <f t="shared" si="2"/>
+        <v>49457.381000000001</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
